--- a/exports/piloto_questoes_autorais_10.xlsx
+++ b/exports/piloto_questoes_autorais_10.xlsx
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUTORAL_Q001</t>
+          <t>ME_AUT_Q001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -575,33 +575,26 @@
           <t>Homem de 68 anos, tabagista de longa data, é submetido a herniorrafia inguinal sob anestesia geral, em decúbito dorsal. No intraoperatório apresenta queda da saturação periférica de oxigênio, revertida com aumento da fração inspirada de oxigênio e manobra de recrutamento. Considerando a relação entre capacidade residual funcional (CRF) e capacidade de fechamento, qual fator melhor explica a maior tendência à hipoxemia desse paciente em comparação a um adulto jovem?</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>A capacidade de fechamento reduz-se progressivamente com a idade, tornando-se menor que a CRF.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>A capacidade de fechamento aumenta com a idade e pode superar a CRF, levando ao fechamento de vias aéreas durante a ventilação corrente.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>A CRF aumenta no decúbito dorsal, e esse aumento aproxima as unidades alveolares da zona 1 de West.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>A capacidade de fechamento não varia com a idade; o determinante isolado da hipoxemia é o aumento do espaço morto anatômico.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>B</t>
@@ -622,7 +615,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Fisiologia respiratória perioperatória — relação CRF/capacidade de fechamento e atelectasia sob anestesia.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 74: Avaliação do Sistema Respiratório • Guyton &amp; Hall, Tratado de Fisiologia Médica, 14ª ed. — cap. 40: Princípios da Troca Gasosa; Difusão de Oxigênio e Dióxido de Carbono pela Membrana Respiratória</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -630,14 +623,16 @@
           <t>Fisiologia e Farmacologia do Sistema Respiratório</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>1</v>
       </c>
@@ -645,7 +640,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AUTORAL_Q002</t>
+          <t>ME_AUT_Q002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -653,33 +648,26 @@
           <t>Antes da indução em sequência rápida de uma paciente de 32 anos, com índice de massa corporal de 24 kg/m², realiza-se pré-oxigenação com máscara facial bem acoplada e oxigênio a 100% por três minutos. Qual é o principal mecanismo pelo qual essa manobra prolonga o tempo até a dessaturação durante o período de apneia?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Aumento expressivo da quantidade de oxigênio dissolvido no plasma.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Elevação da saturação da hemoglobina de 97% para 100%, com ganho proporcional no conteúdo arterial de oxigênio.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Substituição do nitrogênio contido na capacidade residual funcional por oxigênio, criando um reservatório alveolar.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Redução do consumo metabólico de oxigênio pelo miocárdio e pelo sistema nervoso central.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>C</t>
@@ -700,7 +688,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Manejo de via aérea — pré-oxigenação, desnitrogenação e tempo de apneia seguro.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 67: Controle da Via Aérea</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -708,14 +696,16 @@
           <t>Vias Aéreas</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>1</v>
       </c>
@@ -723,7 +713,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUTORAL_Q003</t>
+          <t>ME_AUT_Q003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -731,33 +721,26 @@
           <t>Ao comparar o desflurano, cujo coeficiente de partição sangue/gás é de aproximadamente 0,42, com o isoflurano, cujo coeficiente é de aproximadamente 1,4, qual afirmação está correta quanto à velocidade de indução anestésica?</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>O isoflurano determina indução mais rápida, porque a maior solubilidade sanguínea eleva mais depressamente a pressão parcial alveolar.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>O desflurano determina indução mais rápida, porque a menor solubilidade sanguínea permite elevação mais veloz da pressão parcial alveolar.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>A velocidade de indução depende exclusivamente da concentração alveolar mínima de cada agente.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>A solubilidade sanguínea não influencia a indução; apenas a solubilidade tecidual em gordura o faz.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>B</t>
@@ -778,7 +761,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Farmacologia dos anestésicos inalatórios — captação, distribuição e curva F&lt;sub&gt;A&lt;/sub&gt;/F&lt;sub&gt;I&lt;/sub&gt;.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 41: Farmacocinética dos Anestésicos Inalatórios • Miller's Anesthesia, 10ª ed. — cap. 18: Inhaled Anesthetic Uptake, Distribution, Metabolism, and Toxicity</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -786,14 +769,16 @@
           <t>Farmacologia dos Anestésicos Inalatórios</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>1</v>
       </c>
@@ -801,7 +786,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUTORAL_Q004</t>
+          <t>ME_AUT_Q004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -809,33 +794,26 @@
           <t>Homem de 27 anos, com paraplegia decorrente de trauma raquimedular ocorrido há três semanas, será submetido a desbridamento de úlcera por pressão em região sacral. A equipe considera o uso de succinilcolina para facilitar a intubação. Qual é o principal mecanismo que contraindica esse fármaco nesse contexto?</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Redução da atividade da butirilcolinesterase plasmática, com prolongamento acentuado do bloqueio.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Proliferação de receptores nicotínicos extrajuncionais, com efluxo maciço de potássio após a despolarização.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Maior suscetibilidade ao bloqueio de fase II, com bloqueio residual prolongado no pós-operatório.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Liberação de histamina dependente de dose, com hipotensão refratária a vasopressores.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>B</t>
@@ -856,7 +834,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Bloqueadores neuromusculares — succinilcolina, receptores extrajuncionais e hipercalemia.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 22: Fisiologia da Função Neuromuscular • Stoelting's Pharmacology &amp; Physiology in Anesthetic Practice, 6ª ed. — cap. 12: Neuromuscular-Blocking Drugs and Reversal Agents</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -864,14 +842,16 @@
           <t>Transmissão e Bloqueio Neuromuscular</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>1</v>
       </c>
@@ -879,7 +859,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AUTORAL_Q005</t>
+          <t>TEA_AUT_Q001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -887,33 +867,26 @@
           <t>Durante laparotomia sob anestesia geral, paciente previamente estável apresenta queda súbita do dióxido de carbono ao final da expiração de 35 para 12 mmHg, acompanhada de hipotensão e taquicardia. Gasometria arterial colhida imediatamente revela PaCO₂ de 44 mmHg. O alargamento do gradiente entre a PaCO₂ e o CO₂ expirado nesse cenário sugere principalmente:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Hipoventilação alveolar por bloqueio neuromuscular residual.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Aumento agudo do espaço morto alveolar, como no tromboembolismo pulmonar ou na queda abrupta do débito cardíaco.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Absorção sistêmica de dióxido de carbono proveniente do pneumoperitônio.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Exaustão da cal sodada, com reinalação de dióxido de carbono.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>B</t>
@@ -934,7 +907,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Monitorização — capnografia, gradiente PaCO₂–EtCO₂ e espaço morto alveolar.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 87: Monitorização do Sistema Respiratório</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -942,14 +915,16 @@
           <t>Monitorização</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>TEA</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -957,7 +932,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AUTORAL_Q006</t>
+          <t>TEA_AUT_Q002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -965,33 +940,26 @@
           <t>Gestante de 38 semanas é posicionada em decúbito dorsal horizontal para cesariana eletiva sob raquianestesia. Poucos minutos após o bloqueio, apresenta hipotensão arterial, náusea, palidez e sensação de mal-estar. Além da vasoplegia decorrente do bloqueio simpático, qual medida deve ser adotada imediatamente para corrigir o mecanismo adicional envolvido?</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Posicionar a paciente em Trendelenburg acentuado para aumentar o retorno venoso cerebral.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Realizar deslocamento uterino para a esquerda, aliviando a compressão da veia cava inferior.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Administrar atropina, pois a bradicardia reflexa é a causa predominante do quadro.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Reduzir a fração inspirada de oxigênio, revertendo a vasoconstrição induzida pela hiperóxia.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>B</t>
@@ -1012,7 +980,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Anestesia obstétrica — alterações fisiológicas da gestação e compressão aortocava.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 129: Anestesia para Cesariana</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1020,14 +988,16 @@
           <t>Anestesia em Obstetrícia</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>TEA</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>1</v>
       </c>
@@ -1035,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUTORAL_Q007</t>
+          <t>TEA_AUT_Q003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1043,33 +1013,26 @@
           <t>Paciente de 70 anos, em uso de enoxaparina em dose profilática de 40 mg por via subcutânea a cada 24 horas, será submetido a artroplastia total de joelho sob raquianestesia. Qual é a conduta mais adequada quanto ao intervalo entre a última dose do anticoagulante e a punção neuroaxial?</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>A punção pode ser realizada a qualquer momento, uma vez que se trata de dose profilática.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Deve-se aguardar pelo menos 12 horas após a última dose profilática antes de realizar a punção.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Deve-se aguardar pelo menos 4 horas após a última dose, intervalo suficiente para a depuração do fármaco.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>A raquianestesia está absolutamente contraindicada em qualquer paciente que faça uso de heparina de baixo peso molecular.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>B</t>
@@ -1090,7 +1053,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Anestesia regional em paciente anticoagulado — intervalos de segurança para HBPM.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 114: Complicações dos Bloqueios Regionais</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1098,14 +1061,16 @@
           <t>Hemostasia e Anticoagulação</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>TEA</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>1</v>
       </c>
@@ -1113,7 +1078,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AUTORAL_Q008</t>
+          <t>TSA_AUT_Q001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1121,33 +1086,26 @@
           <t>Homem de 74 anos, portador de estenose aórtica grave com área valvar estimada em 0,7 cm² e gradiente médio elevado, será submetido a colecistectomia videolaparoscópica. Qual conjunto de metas hemodinâmicas é o mais apropriado para a condução anestésica?</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Manter o ritmo sinusal, evitar taquicardia, preservar a pré-carga e sustentar a resistência vascular sistêmica.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Induzir taquicardia moderada, de modo a encurtar o tempo de ejeção e elevar o débito cardíaco.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Reduzir deliberadamente a resistência vascular sistêmica, aliviando a pós-carga do ventrículo esquerdo.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Manter a pré-carga deliberadamente baixa, reduzindo a tensão parietal do ventrículo hipertrofiado.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>A</t>
@@ -1168,7 +1126,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Anestesia em valvopatias — metas hemodinâmicas na estenose aórtica.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 155: Anestesia para Cirurgia Valvar</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1176,14 +1134,16 @@
           <t>Anestesia e Sistema Cardiovascular</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>TSA</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>1</v>
       </c>
@@ -1191,7 +1151,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUTORAL_Q009</t>
+          <t>TSA_AUT_Q002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1199,33 +1159,26 @@
           <t>Paciente com traumatismo cranioencefálico grave encontra-se monitorizado com cateter de pressão intracraniana, que registra 25 mmHg, e pressão arterial média de 80 mmHg. A equipe discute o emprego de hiperventilação para controle da hipertensão intracraniana. Qual afirmação está correta?</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>A hiperventilação deve ser mantida continuamente, com PaCO₂ em torno de 25 mmHg, durante todo o período pós-operatório.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>A hiperventilação reduz a pressão intracraniana por vasoconstrição cerebral, porém seu uso prolongado ou excessivo pode causar isquemia, sendo medida temporária.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>A hiperventilação não altera o fluxo sanguíneo cerebral, atuando exclusivamente sobre a produção de líquido cefalorraquidiano.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>A pressão de perfusão cerebral desse paciente é de 105 mmHg, valor que dispensa qualquer intervenção adicional.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>B</t>
@@ -1246,7 +1199,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Neuroanestesia — fluxo sanguíneo cerebral, reatividade ao CO₂ e manejo da hipertensão intracraniana.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 172: Fatores Determinantes das Pressões Intracranianas e de Perfusão Encefálica</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1254,14 +1207,16 @@
           <t>Anestesia para Neurocirurgia</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>TSA</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>1</v>
       </c>
@@ -1269,7 +1224,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AUTORAL_Q010</t>
+          <t>TSA_AUT_Q003</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1277,33 +1232,26 @@
           <t>Puérpera recebeu 2 mg de morfina por via peridural ao final de cesariana, com boa analgesia nas primeiras horas. Qual é a característica mais importante da depressão respiratória associada a essa via de administração?</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Ocorre exclusivamente nos primeiros 30 minutos, decorrente da absorção vascular rápida a partir do espaço peridural.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Pode manifestar-se de forma tardia, entre 6 e 12 horas após a administração, em razão da migração rostral do opioide no líquido cefalorraquidiano.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Não ocorre com doses inferiores a 5 mg, faixa considerada isenta de risco respiratório.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>É integralmente prevenida pela associação de anti-inflamatórios não esteroidais no esquema analgésico.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>B</t>
@@ -1324,7 +1272,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Dor aguda — opioides neuroaxiais, hidrofilia e depressão respiratória bifásica.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 117: Analgesia Controlada pelo Paciente</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1332,14 +1280,16 @@
           <t>Dor</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>TSA</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>1</v>
       </c>

--- a/exports/piloto_questoes_autorais_10.xlsx
+++ b/exports/piloto_questoes_autorais_10.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;capacidade de fechamento&lt;/strong&gt; é o volume pulmonar a partir do qual as pequenas vias aéreas dependentes começam a se fechar. Ela &lt;strong&gt;aumenta progressivamente com a idade&lt;/strong&gt;, por perda do recolhimento elástico e do suporte radial das vias aéreas — processo acelerado pelo tabagismo.&lt;/p&gt;&lt;p&gt;Em paralelo, a &lt;strong&gt;CRF diminui&lt;/strong&gt; na mudança da posição ortostática para o decúbito dorsal e é ainda mais reduzida pela indução anestésica, pela paralisia diafragmática e pelo deslocamento cefálico do diafragma.&lt;/p&gt;&lt;p&gt;Quando a capacidade de fechamento &lt;strong&gt;ultrapassa a CRF&lt;/strong&gt;, ocorre fechamento de vias aéreas já durante a respiração corrente: as unidades pulmonares distais ficam perfundidas mas mal ventiladas, gerando &lt;strong&gt;distúrbio V/Q e shunt&lt;/strong&gt;, com hipoxemia. Em decúbito dorsal esse cruzamento ocorre por volta dos 45 anos; em posição sentada, por volta dos 65 anos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a capacidade de fechamento aumenta, e não diminui, com a idade (A); a CRF &lt;em&gt;diminui&lt;/em&gt; em decúbito dorsal (C); e o mecanismo predominante aqui é o fechamento de vias aéreas com shunt, não o espaço morto (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;capacidade de fechamento&lt;/strong&gt; é o volume pulmonar a partir do qual as pequenas vias aéreas dependentes começam a se fechar. Ela &lt;strong&gt;aumenta progressivamente com a idade&lt;/strong&gt;, por perda do recolhimento elástico e do suporte radial das vias aéreas, processo acelerado pelo tabagismo.&lt;/p&gt;&lt;p&gt;Em paralelo, a &lt;strong&gt;CRF diminui&lt;/strong&gt; na mudança da posição ortostática para o decúbito dorsal e é ainda mais reduzida pela indução anestésica, pela paralisia diafragmática e pelo deslocamento cefálico do diafragma.&lt;/p&gt;&lt;p&gt;Quando a capacidade de fechamento &lt;strong&gt;ultrapassa a CRF&lt;/strong&gt;, ocorre fechamento de vias aéreas já durante a respiração corrente: as unidades pulmonares distais ficam perfundidas mas mal ventiladas, gerando &lt;strong&gt;distúrbio V/Q e shunt&lt;/strong&gt;, com hipoxemia. Em decúbito dorsal esse cruzamento ocorre por volta dos 45 anos; em posição sentada, por volta dos 65 anos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a capacidade de fechamento aumenta, e não diminui, com a idade (A); a CRF &lt;em&gt;diminui&lt;/em&gt; em decúbito dorsal (C); e o mecanismo predominante aqui é o fechamento de vias aéreas com shunt, não o espaço morto (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;coeficiente de partição sangue/gás&lt;/strong&gt; expressa a avidez do sangue pelo agente. Quanto &lt;strong&gt;menor&lt;/strong&gt; esse coeficiente, menor a quantidade de agente que precisa ser dissolvida no sangue para que a pressão parcial se eleve — e a razão entre a fração alveolar e a fração inspirada (F&lt;sub&gt;A&lt;/sub&gt;/F&lt;sub&gt;I&lt;/sub&gt;) sobe mais rapidamente.&lt;/p&gt;&lt;p&gt;Como é a &lt;strong&gt;pressão parcial alveolar&lt;/strong&gt; que se equilibra com o cérebro, agentes pouco solúveis como o desflurano (0,42) e o óxido nitroso (0,47) produzem indução e despertar mais rápidos que agentes mais solúveis como o isoflurano (1,4) e o halotano (2,4).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cuidado com a armadilha conceitual:&lt;/strong&gt; maior solubilidade sanguínea significa maior captação pelo sangue e, portanto, indução &lt;em&gt;mais lenta&lt;/em&gt; — o oposto do que a intuição sugere (A). A CAM é medida de &lt;strong&gt;potência&lt;/strong&gt;, não de velocidade (C). E a solubilidade em gordura relaciona-se sobretudo à potência e à cinética de despertar após anestesias prolongadas, não à velocidade inicial de indução (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;coeficiente de partição sangue/gás&lt;/strong&gt; expressa a avidez do sangue pelo agente. Quanto &lt;strong&gt;menor&lt;/strong&gt; esse coeficiente, menor a quantidade de agente que precisa ser dissolvida no sangue para que a pressão parcial se eleve, e a razão entre a fração alveolar e a fração inspirada (F&lt;sub&gt;A&lt;/sub&gt;/F&lt;sub&gt;I&lt;/sub&gt;) sobe mais rapidamente.&lt;/p&gt;&lt;p&gt;Como é a &lt;strong&gt;pressão parcial alveolar&lt;/strong&gt; que se equilibra com o cérebro, agentes pouco solúveis como o desflurano (0,42) e o óxido nitroso (0,47) produzem indução e despertar mais rápidos que agentes mais solúveis como o isoflurano (1,4) e o halotano (2,4).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cuidado com a armadilha conceitual:&lt;/strong&gt; maior solubilidade sanguínea significa maior captação pelo sangue e, portanto, indução &lt;em&gt;mais lenta&lt;/em&gt;, o oposto do que a intuição sugere (A). A CAM é medida de &lt;strong&gt;potência&lt;/strong&gt;, não de velocidade (C). E a solubilidade em gordura relaciona-se sobretudo à potência e à cinética de despertar após anestesias prolongadas, não à velocidade inicial de indução (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Após denervação, imobilização prolongada, queimaduras extensas ou lesão medular, ocorre &lt;strong&gt;proliferação (upregulation) de receptores nicotínicos extrajuncionais&lt;/strong&gt; por toda a membrana muscular, incluindo isoformas imaturas com canal de abertura prolongada.&lt;/p&gt;&lt;p&gt;Quando a succinilcolina despolariza essa superfície muito ampliada, o &lt;strong&gt;efluxo de potássio&lt;/strong&gt; é maciço e pode elevar a caliemia em vários mEq/L em poucos minutos, precipitando &lt;strong&gt;arritmias e parada cardíaca hipercalêmica&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O risco começa a se estabelecer por volta de 24 a 72 horas após a lesão e persiste por meses — habitualmente considera-se um período de risco de até 6 a 12 meses ou enquanto durar a denervação. Este paciente, com três semanas de lesão, encontra-se plenamente nessa janela; a escolha adequada é um &lt;strong&gt;bloqueador adespolarizante&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a deficiência de butirilcolinesterase prolonga o bloqueio, mas não é o mecanismo relacionado à lesão medular (A); o bloqueio de fase II decorre de doses altas ou repetidas, não da denervação (C); e a liberação de histamina não é a preocupação central aqui (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Após denervação, imobilização prolongada, queimaduras extensas ou lesão medular, ocorre &lt;strong&gt;proliferação (upregulation) de receptores nicotínicos extrajuncionais&lt;/strong&gt; por toda a membrana muscular, incluindo isoformas imaturas com canal de abertura prolongada.&lt;/p&gt;&lt;p&gt;Quando a succinilcolina despolariza essa superfície muito ampliada, o &lt;strong&gt;efluxo de potássio&lt;/strong&gt; é maciço e pode elevar a caliemia em vários mEq/L em poucos minutos, precipitando &lt;strong&gt;arritmias e parada cardíaca hipercalêmica&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O risco começa a se estabelecer por volta de 24 a 72 horas após a lesão e persiste por meses; habitualmente considera-se um período de risco de até 6 a 12 meses ou enquanto durar a denervação. Este paciente, com três semanas de lesão, encontra-se plenamente nessa janela; a escolha adequada é um &lt;strong&gt;bloqueador adespolarizante&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a deficiência de butirilcolinesterase prolonga o bloqueio, mas não é o mecanismo relacionado à lesão medular (A); o bloqueio de fase II decorre de doses altas ou repetidas, não da denervação (C); e a liberação de histamina não é a preocupação central aqui (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O gradiente normal entre PaCO₂ e EtCO₂ é de 2 a 5 mmHg e reflete o &lt;strong&gt;espaço morto alveolar&lt;/strong&gt; — unidades ventiladas, porém não perfundidas. Neste caso o gradiente saltou para 32 mmHg.&lt;/p&gt;&lt;p&gt;Um &lt;strong&gt;alargamento súbito&lt;/strong&gt; do gradiente, com queda do EtCO₂ e PaCO₂ preservada ou elevada, indica que sangue deixou de chegar a unidades que continuam sendo ventiladas. As causas clássicas são &lt;strong&gt;tromboembolismo pulmonar&lt;/strong&gt; (trombo, ar, gordura, líquido amniótico) e &lt;strong&gt;queda abrupta do débito cardíaco&lt;/strong&gt;, incluindo a parada cardíaca. A associação com hipotensão e taquicardia reforça essa interpretação e exige investigação imediata.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a hipoventilação &lt;em&gt;eleva&lt;/em&gt; o EtCO₂ (A); a absorção de CO₂ do pneumoperitônio também &lt;em&gt;eleva&lt;/em&gt; o EtCO₂ (C); e a exaustão da cal sodada eleva sobretudo a linha de base inspiratória do capnograma, sem produzir queda do EtCO₂ (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;O gradiente normal entre PaCO₂ e EtCO₂ é de 2 a 5 mmHg e reflete o &lt;strong&gt;espaço morto alveolar&lt;/strong&gt;: unidades ventiladas, porém não perfundidas. Neste caso o gradiente saltou para 32 mmHg.&lt;/p&gt;&lt;p&gt;Um &lt;strong&gt;alargamento súbito&lt;/strong&gt; do gradiente, com queda do EtCO₂ e PaCO₂ preservada ou elevada, indica que sangue deixou de chegar a unidades que continuam sendo ventiladas. As causas clássicas são &lt;strong&gt;tromboembolismo pulmonar&lt;/strong&gt; (trombo, ar, gordura, líquido amniótico) e &lt;strong&gt;queda abrupta do débito cardíaco&lt;/strong&gt;, incluindo a parada cardíaca. A associação com hipotensão e taquicardia reforça essa interpretação e exige investigação imediata.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a hipoventilação &lt;em&gt;eleva&lt;/em&gt; o EtCO₂ (A); a absorção de CO₂ do pneumoperitônio também &lt;em&gt;eleva&lt;/em&gt; o EtCO₂ (C); e a exaustão da cal sodada eleva sobretudo a linha de base inspiratória do capnograma, sem produzir queda do EtCO₂ (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A partir do segundo trimestre, o útero gravídico em decúbito dorsal comprime a &lt;strong&gt;veia cava inferior e a aorta&lt;/strong&gt; contra a coluna vertebral. A compressão cava reduz o retorno venoso, o volume sistólico e o débito cardíaco — a chamada &lt;strong&gt;síndrome de hipotensão supina&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Em condições normais a gestante compensa com vasoconstrição simpática e circulação colateral pelo sistema ázigos. A &lt;strong&gt;raquianestesia abole essa compensação&lt;/strong&gt;, de modo que os dois mecanismos se somam e a hipotensão se torna abrupta e sintomática, com risco de redução do fluxo uteroplacentário e sofrimento fetal.&lt;/p&gt;&lt;p&gt;A conduta imediata é o &lt;strong&gt;deslocamento uterino para a esquerda&lt;/strong&gt;, obtido com cunha sob o quadril direito ou inclinação lateral da mesa de pelo menos 15 graus, associado a vasopressor (fenilefrina como primeira escolha) e reposição volêmica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o Trendelenburg acentuado não corrige a compressão mecânica e pode elevar o nível do bloqueio (A); a bradicardia pode ocorrer, mas não é o mecanismo predominante (C); e a fração inspirada de oxigênio não tem relação com o quadro (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A partir do segundo trimestre, o útero gravídico em decúbito dorsal comprime a &lt;strong&gt;veia cava inferior e a aorta&lt;/strong&gt; contra a coluna vertebral. A compressão cava reduz o retorno venoso, o volume sistólico e o débito cardíaco, a chamada &lt;strong&gt;síndrome de hipotensão supina&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Em condições normais a gestante compensa com vasoconstrição simpática e circulação colateral pelo sistema ázigos. A &lt;strong&gt;raquianestesia abole essa compensação&lt;/strong&gt;, de modo que os dois mecanismos se somam e a hipotensão se torna abrupta e sintomática, com risco de redução do fluxo uteroplacentário e sofrimento fetal.&lt;/p&gt;&lt;p&gt;A conduta imediata é o &lt;strong&gt;deslocamento uterino para a esquerda&lt;/strong&gt;, obtido com cunha sob o quadril direito ou inclinação lateral da mesa de pelo menos 15 graus, associado a vasopressor (fenilefrina como primeira escolha) e reposição volêmica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o Trendelenburg acentuado não corrige a compressão mecânica e pode elevar o nível do bloqueio (A); a bradicardia pode ocorrer, mas não é o mecanismo predominante (C); e a fração inspirada de oxigênio não tem relação com o quadro (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na estenose aórtica grave o ventrículo esquerdo é &lt;strong&gt;hipertrofiado, pouco complacente e dependente de pré-carga&lt;/strong&gt;, com débito relativamente fixo através de um orifício valvar estreito.&lt;/p&gt;&lt;p&gt;As metas hemodinâmicas são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ritmo sinusal:&lt;/strong&gt; a contração atrial pode responder por até 40% do enchimento ventricular; a fibrilação atrial costuma ser mal tolerada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar taquicardia:&lt;/strong&gt; encurta a diástole, prejudica o enchimento e reduz a perfusão coronariana de um miocárdio hipertrofiado e vulnerável à isquemia subendocárdica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preservar a pré-carga:&lt;/strong&gt; o ventrículo rígido depende de pressões de enchimento adequadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a resistência vascular sistêmica:&lt;/strong&gt; como o débito é fixo, a queda da RVS não é compensada por aumento do volume sistólico e produz hipotensão profunda, com queda da pressão de perfusão coronariana — podendo instalar o ciclo de isquemia, disfunção e colapso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por essas razões, as alternativas B, C e D descrevem exatamente as condições que devem ser &lt;strong&gt;evitadas&lt;/strong&gt; nesse paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na estenose aórtica grave o ventrículo esquerdo é &lt;strong&gt;hipertrofiado, pouco complacente e dependente de pré-carga&lt;/strong&gt;, com débito relativamente fixo através de um orifício valvar estreito.&lt;/p&gt;&lt;p&gt;As metas hemodinâmicas são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ritmo sinusal:&lt;/strong&gt; a contração atrial pode responder por até 40% do enchimento ventricular; a fibrilação atrial costuma ser mal tolerada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar taquicardia:&lt;/strong&gt; encurta a diástole, prejudica o enchimento e reduz a perfusão coronariana de um miocárdio hipertrofiado e vulnerável à isquemia subendocárdica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preservar a pré-carga:&lt;/strong&gt; o ventrículo rígido depende de pressões de enchimento adequadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a resistência vascular sistêmica:&lt;/strong&gt; como o débito é fixo, a queda da RVS não é compensada por aumento do volume sistólico e produz hipotensão profunda, com queda da pressão de perfusão coronariana, podendo instalar o ciclo de isquemia, disfunção e colapso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por essas razões, as alternativas B, C e D descrevem exatamente as condições que devem ser &lt;strong&gt;evitadas&lt;/strong&gt; nesse paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O fluxo sanguíneo cerebral responde de forma praticamente linear à PaCO₂ na faixa de 20 a 80 mmHg: cada variação de 1 mmHg altera o fluxo em cerca de 1 a 2 mL/100 g/min. A hiperventilação provoca &lt;strong&gt;vasoconstrição cerebral&lt;/strong&gt;, reduz o volume sanguíneo intracraniano e, por consequência, a pressão intracraniana.&lt;/p&gt;&lt;p&gt;O efeito, contudo, é &lt;strong&gt;transitório&lt;/strong&gt;: em 6 a 24 horas o pH liquórico se normaliza por compensação com bicarbonato e a vasoconstrição se dissipa. Pior, a hiperventilação agressiva (PaCO₂ abaixo de 30 mmHg, sobretudo abaixo de 25) pode reduzir o fluxo abaixo do limiar isquêmico em um cérebro já vulnerável, e a normalização abrupta da PaCO₂ depois pode causar hiperemia de rebote.&lt;/p&gt;&lt;p&gt;Por isso a hiperventilação é hoje reservada como &lt;strong&gt;medida de resgate temporária&lt;/strong&gt;, diante de sinais de herniação ou hipertensão intracraniana refratária, enquanto se instituem medidas definitivas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Sobre a alternativa D:&lt;/strong&gt; a pressão de perfusão cerebral é calculada como PAM menos PIC, ou seja, 80 − 25 = &lt;strong&gt;55 mmHg&lt;/strong&gt; — valor abaixo do alvo habitual de 60 a 70 mmHg, que portanto &lt;em&gt;exige&lt;/em&gt; intervenção.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O fluxo sanguíneo cerebral responde de forma praticamente linear à PaCO₂ na faixa de 20 a 80 mmHg: cada variação de 1 mmHg altera o fluxo em cerca de 1 a 2 mL/100 g/min. A hiperventilação provoca &lt;strong&gt;vasoconstrição cerebral&lt;/strong&gt;, reduz o volume sanguíneo intracraniano e, por consequência, a pressão intracraniana.&lt;/p&gt;&lt;p&gt;O efeito, contudo, é &lt;strong&gt;transitório&lt;/strong&gt;: em 6 a 24 horas o pH liquórico se normaliza por compensação com bicarbonato e a vasoconstrição se dissipa. Pior, a hiperventilação agressiva (PaCO₂ abaixo de 30 mmHg, sobretudo abaixo de 25) pode reduzir o fluxo abaixo do limiar isquêmico em um cérebro já vulnerável, e a normalização abrupta da PaCO₂ depois pode causar hiperemia de rebote.&lt;/p&gt;&lt;p&gt;Por isso a hiperventilação é hoje reservada como &lt;strong&gt;medida de resgate temporária&lt;/strong&gt;, diante de sinais de herniação ou hipertensão intracraniana refratária, enquanto se instituem medidas definitivas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Sobre a alternativa D:&lt;/strong&gt; a pressão de perfusão cerebral é calculada como PAM menos PIC, ou seja, 80 − 25 = &lt;strong&gt;55 mmHg&lt;/strong&gt;, valor abaixo do alvo habitual de 60 a 70 mmHg, que portanto &lt;em&gt;exige&lt;/em&gt; intervenção.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A morfina é um opioide &lt;strong&gt;hidrofílico&lt;/strong&gt;. Após a administração neuroaxial, sua permanência prolongada no líquido cefalorraquidiano permite a &lt;strong&gt;migração rostral&lt;/strong&gt; até o tronco encefálico, onde atinge os centros respiratórios bulbares.&lt;/p&gt;&lt;p&gt;Disso resulta o padrão &lt;strong&gt;bifásico&lt;/strong&gt; clássico:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Precoce&lt;/strong&gt; (30 a 90 minutos): por absorção vascular a partir do espaço peridural.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Tardia&lt;/strong&gt; (6 a 12 horas, podendo estender-se até 24 horas): por migração rostral no LCR — é a que mais surpreende a equipe, pois ocorre quando a paciente já saiu da sala de recuperação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso recomenda-se &lt;strong&gt;monitorização respiratória por pelo menos 24 horas&lt;/strong&gt; após morfina neuroaxial, com atenção à frequência respiratória e ao nível de sedação, e cautela redobrada na associação com opioides sistêmicos ou sedativos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Contraste útil:&lt;/strong&gt; opioides &lt;strong&gt;lipofílicos&lt;/strong&gt; como o fentanil e o sufentanil são rapidamente captados pelo tecido neural e pela gordura peridural, produzindo analgesia de instalação mais rápida, duração menor e risco muito reduzido de depressão respiratória tardia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a depressão precoce existe, mas não é exclusiva (A); não há dose isenta de risco, e 2 a 3 mg é justamente a faixa usual em obstetrícia (C); e os anti-inflamatórios reduzem a necessidade de opioide, mas não previnem integralmente a depressão respiratória (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A morfina é um opioide &lt;strong&gt;hidrofílico&lt;/strong&gt;. Após a administração neuroaxial, sua permanência prolongada no líquido cefalorraquidiano permite a &lt;strong&gt;migração rostral&lt;/strong&gt; até o tronco encefálico, onde atinge os centros respiratórios bulbares.&lt;/p&gt;&lt;p&gt;Disso resulta o padrão &lt;strong&gt;bifásico&lt;/strong&gt; clássico:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Precoce&lt;/strong&gt; (30 a 90 minutos): por absorção vascular a partir do espaço peridural.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Tardia&lt;/strong&gt; (6 a 12 horas, podendo estender-se até 24 horas): por migração rostral no LCR; é a que mais surpreende a equipe, pois ocorre quando a paciente já saiu da sala de recuperação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso recomenda-se &lt;strong&gt;monitorização respiratória por pelo menos 24 horas&lt;/strong&gt; após morfina neuroaxial, com atenção à frequência respiratória e ao nível de sedação, e cautela redobrada na associação com opioides sistêmicos ou sedativos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Contraste útil:&lt;/strong&gt; opioides &lt;strong&gt;lipofílicos&lt;/strong&gt; como o fentanil e o sufentanil são rapidamente captados pelo tecido neural e pela gordura peridural, produzindo analgesia de instalação mais rápida, duração menor e risco muito reduzido de depressão respiratória tardia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a depressão precoce existe, mas não é exclusiva (A); não há dose isenta de risco, e 2 a 3 mg é justamente a faixa usual em obstetrícia (C); e os anti-inflamatórios reduzem a necessidade de opioide, mas não previnem integralmente a depressão respiratória (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">

--- a/exports/piloto_questoes_autorais_10.xlsx
+++ b/exports/piloto_questoes_autorais_10.xlsx
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="str">
-        <v>&lt;p&gt;Na estenose aórtica grave o ventrículo esquerdo é &lt;strong&gt;hipertrofiado, pouco complacente e dependente de pré-carga&lt;/strong&gt;, com débito relativamente fixo através de um orifício valvar estreito.&lt;/p&gt;&lt;p&gt;As metas hemodinâmicas são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ritmo sinusal:&lt;/strong&gt; a contração atrial pode responder por até 40% do enchimento ventricular; a fibrilação atrial costuma ser mal tolerada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar taquicardia:&lt;/strong&gt; encurta a diástole, prejudica o enchimento e reduz a perfusão coronariana de um miocárdio hipertrofiado e vulnerável à isquemia subendocárdica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preservar a pré-carga:&lt;/strong&gt; o ventrículo rígido depende de pressões de enchimento adequadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a resistência vascular sistêmica:&lt;/strong&gt; como o débito é fixo, a queda da RVS não é compensada por aumento do volume sistólico e produz hipotensão profunda, com queda da pressão de perfusão coronariana, podendo instalar o ciclo de isquemia, disfunção e colapso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por essas razões, as alternativas B, C e D descrevem exatamente as condições que devem ser &lt;strong&gt;evitadas&lt;/strong&gt; nesse paciente.&lt;/p&gt;</v>
+        <v>&lt;p&gt;Na estenose aórtica grave o ventrículo esquerdo é &lt;strong&gt;hipertrofiado, pouco complacente e dependente de pré-carga&lt;/strong&gt;, com débito relativamente fixo através de um orifício valvar estreito.&lt;/p&gt;&lt;p&gt;As metas hemodinâmicas são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ritmo sinusal:&lt;/strong&gt; a contração atrial pode responder por até 40% do enchimento ventricular; a fibrilação atrial costuma ser mal tolerada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar taquicardia:&lt;/strong&gt; encurta a diástole, prejudica o enchimento e reduz a perfusão coronariana de um miocárdio hipertrofiado e vulnerável à isquemia subendocárdica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preservar a pré-carga:&lt;/strong&gt; o ventrículo rígido depende de pressões de enchimento adequadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a resistência vascular sistêmica:&lt;/strong&gt; como o débito é fixo, a queda da RVS não é compensada por aumento do volume sistólico e produz hipotensão profunda, com queda da pressão de perfusão coronariana, podendo instalar o ciclo de isquemia, disfunção e colapso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por essas razões, as alternativas que propõem induzir taquicardia, reduzir deliberadamente a resistência vascular sistêmica ou manter a pré-carga baixa descrevem exatamente as condições que devem ser &lt;strong&gt;evitadas&lt;/strong&gt; nesse paciente.&lt;/p&gt;</v>
       </c>
       <c r="Q9" t="str">
         <v>ia</v>
